--- a/samples/wildling/기획데이터/World.xlsx
+++ b/samples/wildling/기획데이터/World.xlsx
@@ -1390,6 +1390,9 @@
     <t xml:space="preserve">Rare</t>
   </si>
   <si>
+    <t xml:space="preserve">Hidden</t>
+  </si>
+  <si>
     <t xml:space="preserve">elder_bark_2</t>
   </si>
   <si>
@@ -1406,9 +1409,6 @@
   </si>
   <si>
     <t xml:space="preserve">brine_otter_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hidden</t>
   </si>
   <si>
     <t xml:space="preserve">enc_ashen_crater</t>
@@ -6234,18 +6234,18 @@
         <v>15</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="15">
       <c r="E15" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F15" s="6">
         <v>2</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="16">
@@ -6448,13 +6448,13 @@
     </row>
     <row r="34">
       <c r="B34" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>39</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>184</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="35">
       <c r="E35" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F35" s="6">
         <v>13</v>
@@ -6501,7 +6501,7 @@
     </row>
     <row r="38">
       <c r="E38" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F38" s="5">
         <v>166</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="41">
       <c r="E41" s="6" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F41" s="6">
         <v>50</v>
@@ -6551,7 +6551,7 @@
         <v>15</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="43">
@@ -6749,7 +6749,7 @@
         <v>2</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="61">
@@ -6857,7 +6857,7 @@
         <v>15</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="70">
@@ -6989,7 +6989,7 @@
         <v>2</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="82">
@@ -7163,7 +7163,7 @@
         <v>15</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="97">
@@ -7229,7 +7229,7 @@
         <v>2</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="103">
@@ -7480,7 +7480,7 @@
         <v>2</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="125">
@@ -7491,7 +7491,7 @@
         <v>1</v>
       </c>
       <c r="G125" s="6" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="126">

--- a/samples/wildling/기획데이터/World.xlsx
+++ b/samples/wildling/기획데이터/World.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="475">
   <si>
     <t xml:space="preserve">:table Region</t>
   </si>
@@ -1354,22 +1354,10 @@
     <t xml:space="preserve">entries[].encounter_slot</t>
   </si>
   <si>
-    <t xml:space="preserve">foreign Monster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EncounterSlot</t>
+    <t xml:space="preserve">EncounterEntry</t>
   </si>
   <si>
     <t xml:space="preserve">은둔 슬롯의 조건</t>
-  </si>
-  <si>
-    <t xml:space="preserve">어느 단계가 나오는가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가중치</t>
-  </si>
-  <si>
-    <t xml:space="preserve">어느 슬롯에서 나오는가</t>
   </si>
   <si>
     <t xml:space="preserve">enc_weir_forest</t>
@@ -6076,12 +6064,8 @@
       <c r="E3" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>444</v>
-      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
@@ -6094,17 +6078,11 @@
         <v>74</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>448</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
@@ -6122,22 +6100,18 @@
       <c r="E5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>30</v>
-      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6">
       <c r="B6" s="5" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>32</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>118</v>
@@ -6151,7 +6125,7 @@
     </row>
     <row r="7">
       <c r="E7" s="6" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="F7" s="6">
         <v>166</v>
@@ -6184,7 +6158,7 @@
     </row>
     <row r="10">
       <c r="E10" s="5" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="F10" s="5">
         <v>50</v>
@@ -6206,7 +6180,7 @@
     </row>
     <row r="12">
       <c r="E12" s="5" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="F12" s="5">
         <v>50</v>
@@ -6223,7 +6197,7 @@
         <v>80</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="14">
@@ -6234,18 +6208,18 @@
         <v>15</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="15">
       <c r="E15" s="6" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="F15" s="6">
         <v>2</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="16">
@@ -6256,7 +6230,7 @@
         <v>80</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="17">
@@ -6311,7 +6285,7 @@
         <v>15</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="22">
@@ -6366,7 +6340,7 @@
         <v>80</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="27">
@@ -6377,7 +6351,7 @@
         <v>15</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="28">
@@ -6421,7 +6395,7 @@
         <v>80</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="32">
@@ -6432,7 +6406,7 @@
         <v>80</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="33">
@@ -6443,18 +6417,18 @@
         <v>15</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="5" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>39</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>184</v>
@@ -6463,18 +6437,18 @@
         <v>80</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="35">
       <c r="E35" s="6" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F35" s="6">
         <v>13</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="36">
@@ -6501,7 +6475,7 @@
     </row>
     <row r="38">
       <c r="E38" s="5" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="F38" s="5">
         <v>166</v>
@@ -6534,7 +6508,7 @@
     </row>
     <row r="41">
       <c r="E41" s="6" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="F41" s="6">
         <v>50</v>
@@ -6551,7 +6525,7 @@
         <v>15</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="43">
@@ -6606,7 +6580,7 @@
         <v>80</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="48">
@@ -6617,7 +6591,7 @@
         <v>15</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="49">
@@ -6661,7 +6635,7 @@
         <v>80</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="53">
@@ -6672,7 +6646,7 @@
         <v>80</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="54">
@@ -6683,7 +6657,7 @@
         <v>15</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="55">
@@ -6727,7 +6701,7 @@
         <v>80</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="59">
@@ -6738,7 +6712,7 @@
         <v>15</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="60">
@@ -6749,18 +6723,18 @@
         <v>2</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="6" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>46</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>248</v>
@@ -6774,7 +6748,7 @@
     </row>
     <row r="62">
       <c r="E62" s="5" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="F62" s="5">
         <v>50</v>
@@ -6807,7 +6781,7 @@
     </row>
     <row r="65">
       <c r="E65" s="6" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="F65" s="6">
         <v>166</v>
@@ -6835,18 +6809,18 @@
         <v>80</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="68">
       <c r="E68" s="5" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="F68" s="5">
         <v>13</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="69">
@@ -6857,7 +6831,7 @@
         <v>15</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="70">
@@ -6901,7 +6875,7 @@
         <v>80</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="74">
@@ -6912,7 +6886,7 @@
         <v>80</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="75">
@@ -6923,7 +6897,7 @@
         <v>15</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="76">
@@ -6967,7 +6941,7 @@
         <v>80</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="80">
@@ -6978,7 +6952,7 @@
         <v>15</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="81">
@@ -6989,7 +6963,7 @@
         <v>2</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="82">
@@ -7044,7 +7018,7 @@
         <v>80</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="87">
@@ -7055,18 +7029,18 @@
         <v>15</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="5" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>52</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="E88" s="5" t="s">
         <v>312</v>
@@ -7091,7 +7065,7 @@
     </row>
     <row r="90">
       <c r="E90" s="5" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="F90" s="5">
         <v>50</v>
@@ -7113,7 +7087,7 @@
     </row>
     <row r="92">
       <c r="E92" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="F92" s="5">
         <v>50</v>
@@ -7130,18 +7104,18 @@
         <v>80</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="94">
       <c r="E94" s="5" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="F94" s="5">
         <v>13</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="95">
@@ -7152,7 +7126,7 @@
         <v>80</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="96">
@@ -7163,7 +7137,7 @@
         <v>15</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="97">
@@ -7207,7 +7181,7 @@
         <v>80</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="101">
@@ -7218,7 +7192,7 @@
         <v>15</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="102">
@@ -7229,7 +7203,7 @@
         <v>2</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="103">
@@ -7284,7 +7258,7 @@
         <v>80</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="108">
@@ -7295,7 +7269,7 @@
         <v>15</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="109">
@@ -7306,7 +7280,7 @@
         <v>80</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="110">
@@ -7361,18 +7335,18 @@
         <v>15</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="115">
       <c r="B115" s="6" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="E115" s="6" t="s">
         <v>376</v>
@@ -7397,7 +7371,7 @@
     </row>
     <row r="117">
       <c r="E117" s="6" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="F117" s="6">
         <v>50</v>
@@ -7419,7 +7393,7 @@
     </row>
     <row r="119">
       <c r="E119" s="6" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="F119" s="6">
         <v>50</v>
@@ -7436,18 +7410,18 @@
         <v>80</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="121">
       <c r="E121" s="6" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="F121" s="6">
         <v>13</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="122">
@@ -7458,18 +7432,18 @@
         <v>15</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="123">
       <c r="E123" s="6" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="F123" s="6">
         <v>2</v>
       </c>
       <c r="G123" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="124">
@@ -7480,18 +7454,18 @@
         <v>2</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="125">
       <c r="E125" s="6" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="F125" s="6">
         <v>1</v>
       </c>
       <c r="G125" s="6" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="126">
@@ -7546,7 +7520,7 @@
         <v>80</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="131">
@@ -7557,7 +7531,7 @@
         <v>15</v>
       </c>
       <c r="G131" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="132">
@@ -7568,7 +7542,7 @@
         <v>80</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="133">
@@ -7623,7 +7597,7 @@
         <v>15</v>
       </c>
       <c r="G137" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="138">
@@ -7678,7 +7652,7 @@
         <v>80</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="143">
@@ -7689,7 +7663,7 @@
         <v>15</v>
       </c>
       <c r="G143" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
